--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="189">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/moped-ext-LKFPunkte</t>
+    <t>https://elga.moped.at/StructureDefinition/moped-ext-LKFPunkte</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -129,7 +129,10 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Element</t>
+    <t>element:https://elga.moped.at/StructureDefinition/MopedLKFRequest#Claim</t>
+  </si>
+  <si>
+    <t>element:https://elga.moped.at/StructureDefinition/MopedLKFResponse#ClaimResponse</t>
   </si>
   <si>
     <t>ID</t>
@@ -722,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -889,6 +892,14 @@
       </c>
       <c r="B21" t="s" s="2">
         <v>38</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -941,115 +952,115 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
@@ -1065,10 +1076,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1080,7 +1091,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -1140,16 +1151,16 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>20</v>
@@ -1157,10 +1168,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1168,10 +1179,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1183,13 +1194,13 @@
         <v>20</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1240,41 +1251,41 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ3" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1286,16 +1297,16 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1333,55 +1344,55 @@
         <v>20</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
@@ -1393,13 +1404,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1450,19 +1461,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1470,10 +1481,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1481,10 +1492,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1496,13 +1507,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1553,30 +1564,30 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1584,10 +1595,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1599,13 +1610,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1644,31 +1655,31 @@
         <v>20</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -1676,10 +1687,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1687,10 +1698,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1702,16 +1713,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1719,7 +1730,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>20</v>
@@ -1761,13 +1772,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -1776,15 +1787,15 @@
         <v>20</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1792,10 +1803,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -1807,13 +1818,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1864,43 +1875,43 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -1912,13 +1923,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1969,19 +1980,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -1989,10 +2000,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2000,10 +2011,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -2015,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2072,30 +2083,30 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2103,10 +2114,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2118,13 +2129,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2163,31 +2174,31 @@
         <v>20</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -2195,10 +2206,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2206,10 +2217,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2221,16 +2232,16 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2238,7 +2249,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>20</v>
@@ -2280,13 +2291,13 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
@@ -2295,15 +2306,15 @@
         <v>20</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2311,10 +2322,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2326,13 +2337,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2383,43 +2394,43 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -2431,13 +2442,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2488,19 +2499,19 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -2508,10 +2519,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2519,10 +2530,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -2534,13 +2545,13 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2591,30 +2602,30 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2622,10 +2633,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -2637,13 +2648,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2682,31 +2693,31 @@
         <v>20</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -2714,10 +2725,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2725,10 +2736,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -2740,16 +2751,16 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2757,7 +2768,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>20</v>
@@ -2799,13 +2810,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -2814,15 +2825,15 @@
         <v>20</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2830,10 +2841,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -2845,13 +2856,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2902,43 +2913,43 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -2950,13 +2961,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3007,19 +3018,19 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
@@ -3027,10 +3038,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3038,10 +3049,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3053,13 +3064,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3110,30 +3121,30 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3141,10 +3152,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -3156,13 +3167,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3201,31 +3212,31 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -3233,10 +3244,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3244,10 +3255,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -3259,16 +3270,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3276,7 +3287,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>20</v>
@@ -3318,13 +3329,13 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -3333,15 +3344,15 @@
         <v>20</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3349,10 +3360,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -3364,13 +3375,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3421,43 +3432,43 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -3469,13 +3480,13 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3526,19 +3537,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -3546,10 +3557,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3557,10 +3568,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -3572,13 +3583,13 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3629,30 +3640,30 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3660,10 +3671,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -3675,13 +3686,13 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3720,31 +3731,31 @@
         <v>20</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -3752,10 +3763,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3763,10 +3774,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -3778,16 +3789,16 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3795,7 +3806,7 @@
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>20</v>
@@ -3837,13 +3848,13 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
@@ -3852,15 +3863,15 @@
         <v>20</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3868,10 +3879,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -3883,13 +3894,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3940,43 +3951,43 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -3988,13 +3999,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4045,19 +4056,19 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -4065,10 +4076,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4076,10 +4087,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -4091,13 +4102,13 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4148,30 +4159,30 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4179,10 +4190,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -4194,13 +4205,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4239,31 +4250,31 @@
         <v>20</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -4271,10 +4282,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4282,10 +4293,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -4297,16 +4308,16 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4314,7 +4325,7 @@
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>20</v>
@@ -4356,13 +4367,13 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -4371,15 +4382,15 @@
         <v>20</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4387,10 +4398,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -4402,13 +4413,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4459,43 +4470,43 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -4507,13 +4518,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4564,19 +4575,19 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -4584,10 +4595,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4595,10 +4606,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -4610,13 +4621,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4667,30 +4678,30 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4698,10 +4709,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -4713,13 +4724,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4758,31 +4769,31 @@
         <v>20</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -4790,10 +4801,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4801,10 +4812,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -4816,16 +4827,16 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -4833,7 +4844,7 @@
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>20</v>
@@ -4875,13 +4886,13 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
@@ -4890,15 +4901,15 @@
         <v>20</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4906,10 +4917,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -4921,13 +4932,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4978,43 +4989,43 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -5026,13 +5037,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5083,19 +5094,19 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -5103,10 +5114,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5114,10 +5125,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -5129,13 +5140,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5186,30 +5197,30 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5217,10 +5228,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -5232,13 +5243,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5277,31 +5288,31 @@
         <v>20</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
@@ -5309,10 +5320,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5320,10 +5331,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -5335,16 +5346,16 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5352,7 +5363,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>20</v>
@@ -5394,13 +5405,13 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
@@ -5409,15 +5420,15 @@
         <v>20</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5425,10 +5436,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -5440,13 +5451,13 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5497,43 +5508,43 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -5545,13 +5556,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5602,19 +5613,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -5622,10 +5633,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5633,10 +5644,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -5648,13 +5659,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5705,30 +5716,30 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5736,10 +5747,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -5751,13 +5762,13 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5796,31 +5807,31 @@
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -5828,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5839,10 +5850,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -5854,16 +5865,16 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -5871,7 +5882,7 @@
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>20</v>
@@ -5913,13 +5924,13 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
@@ -5928,15 +5939,15 @@
         <v>20</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -5944,10 +5955,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -5959,13 +5970,13 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6016,30 +6027,30 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6047,10 +6058,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -6062,16 +6073,16 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6121,13 +6132,13 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
@@ -6136,15 +6147,15 @@
         <v>20</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6152,10 +6163,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -6167,13 +6178,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6224,22 +6235,22 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:36:14+00:00</t>
+    <t>2025-02-20T20:13:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:13:59+00:00</t>
+    <t>2025-02-20T20:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:24:20+00:00</t>
+    <t>2025-02-27T10:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:01:21+00:00</t>
+    <t>2025-02-27T10:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:07:48+00:00</t>
+    <t>2025-03-01T14:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:47:03+00:00</t>
+    <t>2025-03-01T14:53:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:53:36+00:00</t>
+    <t>2025-03-01T15:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T15:19:11+00:00</t>
+    <t>2025-03-02T20:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:51:11+00:00</t>
+    <t>2025-03-02T20:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:57:05+00:00</t>
+    <t>2025-03-11T16:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:13:30+00:00</t>
+    <t>2025-03-11T16:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:22:04+00:00</t>
+    <t>2025-03-12T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-LKFPunkte.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T12:46:26+00:00</t>
+    <t>2025-03-12T14:39:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
